--- a/docs/volts_to_adc.xlsx
+++ b/docs/volts_to_adc.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\UltraZohm\pcb_design\uz_per_sic_inverter_828xcc\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CDEA0FB2-1E91-49ED-A193-A7BD7D0247D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C229371-8406-486D-9A94-FB75C02EE40A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="67080" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{7228B6C1-6041-4CB5-8AFD-AFF5B824FE5A}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7228B6C1-6041-4CB5-8AFD-AFF5B824FE5A}"/>
   </bookViews>
   <sheets>
     <sheet name="Tabelle1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
   <si>
     <t>v_dc</t>
   </si>
@@ -81,6 +81,15 @@
   </si>
   <si>
     <t>Gemäß docs ADC Rauschen max 2,5 mV</t>
+  </si>
+  <si>
+    <t>measured @ #1 Hardware</t>
+  </si>
+  <si>
+    <t>measured @ #2 Hardware</t>
+  </si>
+  <si>
+    <t>v_dc multimeter</t>
   </si>
 </sst>
 </file>
@@ -379,6 +388,1004 @@
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
               <c16:uniqueId val="{00000002-D7D3-4A58-AE22-CAC7BF79CBFF}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Tabelle1!$F$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>measured @ #1 Hardware</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="0.28458394486327054"/>
+                  <c:y val="8.5578455559679495E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr>
+                      <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1">
+                            <a:lumMod val="65000"/>
+                            <a:lumOff val="35000"/>
+                          </a:schemeClr>
+                        </a:solidFill>
+                        <a:latin typeface="+mn-lt"/>
+                        <a:ea typeface="+mn-ea"/>
+                        <a:cs typeface="+mn-cs"/>
+                      </a:defRPr>
+                    </a:pPr>
+                    <a:r>
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:t>#1: y = 140,27x + 450,25</a:t>
+                    </a:r>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="de-DE"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Tabelle1!$F$3:$F$62</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="60"/>
+                <c:pt idx="0">
+                  <c:v>-3.1360000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-3.0640000000000001</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-2.9940000000000002</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-2.923</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-2.8519999999999999</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-2.778</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-2.7080000000000002</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-2.637</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-2.5649999999999999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-2.492</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-2.4209999999999998</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-2.35</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-2.2770000000000001</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-2.206</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-2.1360000000000001</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-2.0640000000000001</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-1.9910000000000001</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-1.92</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-1.8480000000000001</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-1.7769999999999999</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-1.704</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-1.633</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-1.5609999999999999</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-1.488</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>-1.4179999999999999</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>-1.3480000000000001</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>-1.278</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>-1.2070000000000001</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>-1.137</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>-1.0660000000000001</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>-0.995</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>-0.92200000000000004</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>-0.85</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>-0.77900000000000003</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>-0.70599999999999996</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>-0.63600000000000001</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>-0.56299999999999994</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>-0.49399999999999999</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>-0.42</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>-0.34699999999999998</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>-0.27800000000000002</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>-0.21</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>-0.13700000000000001</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>-6.9000000000000006E-2</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>3.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>7.3999999999999996E-2</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.14699999999999999</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.219</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.28799999999999998</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.36199999999999999</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.432</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.504</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.57399999999999995</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.64500000000000002</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.71499999999999997</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.78600000000000003</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.85599999999999998</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.92700000000000005</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.99299999999999999</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>1.052</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Tabelle1!$E$3:$E$62</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="60"/>
+                <c:pt idx="0">
+                  <c:v>10.8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20.7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>30.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>40.6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>60.8</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>70.8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>80.7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>90.7</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>100.9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>110.9</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>120.9</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>131</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>141</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>150.80000000000001</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>160.80000000000001</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>171</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>181</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>190.9</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>200.8</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>211</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>220.9</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>230.9</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>241.1</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>251</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>260.8</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>270.60000000000002</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>280.7</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>290.5</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>300.39999999999998</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>310.39999999999998</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>320.60000000000002</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>330.7</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>340.7</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>350.9</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>360.7</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>371</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>380.6</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>391</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>401.1</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>410.9</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>420.6</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>430.8</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>440.7</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>450.6</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>460.6</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>470.8</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>480.8</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>490.7</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>500.9</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>510.8</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>520.70000000000005</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>530.5</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>540.5</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>550.29999999999995</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>560.29999999999995</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>570.4</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>580.70000000000005</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>590.70000000000005</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>601</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-DC4C-4A09-8EC3-594FC227279E}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Tabelle1!$G$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>measured @ #2 Hardware</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:layout>
+                <c:manualLayout>
+                  <c:x val="-0.16860238025898186"/>
+                  <c:y val="-2.4761925082318944E-2"/>
+                </c:manualLayout>
+              </c:layout>
+              <c:tx>
+                <c:rich>
+                  <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                  <a:lstStyle/>
+                  <a:p>
+                    <a:pPr>
+                      <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                        <a:solidFill>
+                          <a:schemeClr val="tx1">
+                            <a:lumMod val="65000"/>
+                            <a:lumOff val="35000"/>
+                          </a:schemeClr>
+                        </a:solidFill>
+                        <a:latin typeface="+mn-lt"/>
+                        <a:ea typeface="+mn-ea"/>
+                        <a:cs typeface="+mn-cs"/>
+                      </a:defRPr>
+                    </a:pPr>
+                    <a:r>
+                      <a:rPr lang="en-US" baseline="0"/>
+                      <a:t>#2: y = 141,28x + 452,17</a:t>
+                    </a:r>
+                    <a:endParaRPr lang="en-US"/>
+                  </a:p>
+                </c:rich>
+              </c:tx>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="de-DE"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Tabelle1!$G$3:$G$62</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="60"/>
+                <c:pt idx="0">
+                  <c:v>-3.13</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>-3.0579999999999998</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>-2.9889999999999999</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>-2.9169999999999998</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>-2.847</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>-2.774</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>-2.7029999999999998</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>-2.633</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>-2.5619999999999998</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>-2.4889999999999999</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>-2.4180000000000001</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>-2.347</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>-2.2759999999999998</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>-2.2050000000000001</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>-2.1349999999999998</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>-2.0630000000000002</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>-1.9910000000000001</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>-1.92</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>-1.849</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>-1.7789999999999999</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>-1.706</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>-1.635</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>-1.5640000000000001</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>-1.492</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>-1.421</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>-1.3520000000000001</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>-1.2829999999999999</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>-1.2110000000000001</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>-1.141</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>-1.071</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>-1</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>-0.92700000000000005</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>-0.85599999999999998</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>-0.78500000000000003</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>-0.71299999999999997</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>-0.64300000000000002</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>-0.56999999999999995</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>-0.502</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>-0.42799999999999999</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>-0.35599999999999998</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>-0.28599999999999998</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>-0.218</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>-0.14499999999999999</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>-7.5999999999999998E-2</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>-6.0000000000000001E-3</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>6.8000000000000005E-2</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>0.14000000000000001</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>0.20799999999999999</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>0.27700000000000002</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>0.35</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>0.42</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>0.49099999999999999</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>0.56000000000000005</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>0.63</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>0.69899999999999995</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>0.76900000000000002</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>0.83599999999999997</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>0.9</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>0.95</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>0.99099999999999999</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Tabelle1!$E$3:$E$62</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="60"/>
+                <c:pt idx="0">
+                  <c:v>10.8</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>20.7</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>30.5</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>40.6</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>50.5</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>60.8</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>70.8</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>80.7</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>90.7</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>100.9</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>110.9</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>120.9</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>131</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>141</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>150.80000000000001</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>160.80000000000001</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>171</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>181</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>190.9</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>200.8</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>211</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>220.9</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>230.9</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>241.1</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>251</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>260.8</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>270.60000000000002</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>280.7</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>290.5</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>300.39999999999998</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>310.39999999999998</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>320.60000000000002</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>330.7</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>340.7</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>350.9</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>360.7</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>371</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>380.6</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>391</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>401.1</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>410.9</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>420.6</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>430.8</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>440.7</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>450.6</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>460.6</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>470.8</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>480.8</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>490.7</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>500.9</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>510.8</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>520.70000000000005</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>530.5</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>540.5</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>550.29999999999995</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>560.29999999999995</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>570.4</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>580.70000000000005</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>590.70000000000005</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>601</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000004-DC4C-4A09-8EC3-594FC227279E}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -1270,16 +2277,16 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>3</xdr:col>
-      <xdr:colOff>120649</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>112711</xdr:rowOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>122237</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>123824</xdr:colOff>
-      <xdr:row>20</xdr:row>
-      <xdr:rowOff>57149</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>57151</xdr:colOff>
+      <xdr:row>23</xdr:row>
+      <xdr:rowOff>101601</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -1604,221 +2611,910 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BFAE5C3-A2B0-48AC-B53B-0DCCCF3AAB41}">
-  <dimension ref="A1:G44"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="19.08984375" customWidth="1"/>
+    <col min="3" max="3" width="22.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="22.81640625" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>0</v>
       </c>
       <c r="B1" t="s">
         <v>1</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C1" t="s">
+        <v>15</v>
+      </c>
+      <c r="E1" t="s">
+        <v>17</v>
+      </c>
+      <c r="F1" t="s">
+        <v>15</v>
+      </c>
+      <c r="G1" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2">
         <v>0</v>
       </c>
       <c r="B2">
         <v>-4.5</v>
       </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="E2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3">
         <v>100</v>
       </c>
       <c r="B3">
         <v>-3.4990000000000001</v>
       </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C3">
+        <v>-2.4929999999999999</v>
+      </c>
+      <c r="E3">
+        <v>10.8</v>
+      </c>
+      <c r="F3">
+        <v>-3.1360000000000001</v>
+      </c>
+      <c r="G3">
+        <v>-3.13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4">
         <v>200</v>
       </c>
       <c r="B4">
         <v>-2.4990000000000001</v>
       </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C4">
+        <v>-1.7789999999999999</v>
+      </c>
+      <c r="E4">
+        <v>20.7</v>
+      </c>
+      <c r="F4">
+        <v>-3.0640000000000001</v>
+      </c>
+      <c r="G4">
+        <v>-3.0579999999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5">
         <v>282.5</v>
       </c>
       <c r="B5">
         <v>-1.675</v>
       </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C5">
+        <v>-1.202</v>
+      </c>
+      <c r="E5">
+        <v>30.5</v>
+      </c>
+      <c r="F5">
+        <v>-2.9940000000000002</v>
+      </c>
+      <c r="G5">
+        <v>-2.9889999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6">
         <v>300</v>
       </c>
       <c r="B6">
         <v>-1.4990000000000001</v>
       </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C6">
+        <v>-1.0669999999999999</v>
+      </c>
+      <c r="E6">
+        <v>40.6</v>
+      </c>
+      <c r="F6">
+        <v>-2.923</v>
+      </c>
+      <c r="G6">
+        <v>-2.9169999999999998</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7">
         <v>400</v>
       </c>
       <c r="B7">
         <v>-0.499</v>
       </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C7">
+        <v>-0.35199999999999998</v>
+      </c>
+      <c r="E7">
+        <v>50.5</v>
+      </c>
+      <c r="F7">
+        <v>-2.8519999999999999</v>
+      </c>
+      <c r="G7">
+        <v>-2.847</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8">
         <v>500</v>
       </c>
       <c r="B8">
         <v>0.5</v>
       </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C8">
+        <v>0.36</v>
+      </c>
+      <c r="E8">
+        <v>60.8</v>
+      </c>
+      <c r="F8">
+        <v>-2.778</v>
+      </c>
+      <c r="G8">
+        <v>-2.774</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9">
         <v>565</v>
       </c>
       <c r="B9">
         <v>1.151</v>
       </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C9">
+        <v>0.82199999999999995</v>
+      </c>
+      <c r="E9">
+        <v>70.8</v>
+      </c>
+      <c r="F9">
+        <v>-2.7080000000000002</v>
+      </c>
+      <c r="G9">
+        <v>-2.7029999999999998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10">
         <v>600</v>
       </c>
       <c r="B10">
         <v>1.5009999999999999</v>
       </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="C10">
+        <v>1.073</v>
+      </c>
+      <c r="E10">
+        <v>80.7</v>
+      </c>
+      <c r="F10">
+        <v>-2.637</v>
+      </c>
+      <c r="G10">
+        <v>-2.633</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11">
         <v>700</v>
       </c>
       <c r="B11">
         <v>2.5</v>
       </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="E11">
+        <v>90.7</v>
+      </c>
+      <c r="F11">
+        <v>-2.5649999999999999</v>
+      </c>
+      <c r="G11">
+        <v>-2.5619999999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12">
         <v>800</v>
       </c>
       <c r="B12">
         <v>3.4990000000000001</v>
       </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+      <c r="E12">
+        <v>100.9</v>
+      </c>
+      <c r="F12">
+        <v>-2.492</v>
+      </c>
+      <c r="G12">
+        <v>-2.4889999999999999</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13">
         <v>900</v>
       </c>
       <c r="B13">
         <v>4.4980000000000002</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A22" s="1"/>
-    </row>
-    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A28" t="s">
+      <c r="E13">
+        <v>110.9</v>
+      </c>
+      <c r="F13">
+        <v>-2.4209999999999998</v>
+      </c>
+      <c r="G13">
+        <v>-2.4180000000000001</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E14">
+        <v>120.9</v>
+      </c>
+      <c r="F14">
+        <v>-2.35</v>
+      </c>
+      <c r="G14">
+        <v>-2.347</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E15">
+        <v>131</v>
+      </c>
+      <c r="F15">
+        <v>-2.2770000000000001</v>
+      </c>
+      <c r="G15">
+        <v>-2.2759999999999998</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E16">
+        <v>141</v>
+      </c>
+      <c r="F16">
+        <v>-2.206</v>
+      </c>
+      <c r="G16">
+        <v>-2.2050000000000001</v>
+      </c>
+    </row>
+    <row r="17" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E17">
+        <v>150.80000000000001</v>
+      </c>
+      <c r="F17">
+        <v>-2.1360000000000001</v>
+      </c>
+      <c r="G17">
+        <v>-2.1349999999999998</v>
+      </c>
+    </row>
+    <row r="18" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E18">
+        <v>160.80000000000001</v>
+      </c>
+      <c r="F18">
+        <v>-2.0640000000000001</v>
+      </c>
+      <c r="G18">
+        <v>-2.0630000000000002</v>
+      </c>
+    </row>
+    <row r="19" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E19">
+        <v>171</v>
+      </c>
+      <c r="F19">
+        <v>-1.9910000000000001</v>
+      </c>
+      <c r="G19">
+        <v>-1.9910000000000001</v>
+      </c>
+    </row>
+    <row r="20" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E20">
+        <v>181</v>
+      </c>
+      <c r="F20">
+        <v>-1.92</v>
+      </c>
+      <c r="G20">
+        <v>-1.92</v>
+      </c>
+    </row>
+    <row r="21" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E21">
+        <v>190.9</v>
+      </c>
+      <c r="F21">
+        <v>-1.8480000000000001</v>
+      </c>
+      <c r="G21">
+        <v>-1.849</v>
+      </c>
+    </row>
+    <row r="22" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E22">
+        <v>200.8</v>
+      </c>
+      <c r="F22">
+        <v>-1.7769999999999999</v>
+      </c>
+      <c r="G22">
+        <v>-1.7789999999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E23">
+        <v>211</v>
+      </c>
+      <c r="F23">
+        <v>-1.704</v>
+      </c>
+      <c r="G23">
+        <v>-1.706</v>
+      </c>
+    </row>
+    <row r="24" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E24">
+        <v>220.9</v>
+      </c>
+      <c r="F24">
+        <v>-1.633</v>
+      </c>
+      <c r="G24">
+        <v>-1.635</v>
+      </c>
+    </row>
+    <row r="25" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E25">
+        <v>230.9</v>
+      </c>
+      <c r="F25">
+        <v>-1.5609999999999999</v>
+      </c>
+      <c r="G25">
+        <v>-1.5640000000000001</v>
+      </c>
+    </row>
+    <row r="26" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E26">
+        <v>241.1</v>
+      </c>
+      <c r="F26">
+        <v>-1.488</v>
+      </c>
+      <c r="G26">
+        <v>-1.492</v>
+      </c>
+    </row>
+    <row r="27" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E27">
+        <v>251</v>
+      </c>
+      <c r="F27">
+        <v>-1.4179999999999999</v>
+      </c>
+      <c r="G27">
+        <v>-1.421</v>
+      </c>
+    </row>
+    <row r="28" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E28">
+        <v>260.8</v>
+      </c>
+      <c r="F28">
+        <v>-1.3480000000000001</v>
+      </c>
+      <c r="G28">
+        <v>-1.3520000000000001</v>
+      </c>
+    </row>
+    <row r="29" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E29">
+        <v>270.60000000000002</v>
+      </c>
+      <c r="F29">
+        <v>-1.278</v>
+      </c>
+      <c r="G29">
+        <v>-1.2829999999999999</v>
+      </c>
+    </row>
+    <row r="30" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E30">
+        <v>280.7</v>
+      </c>
+      <c r="F30">
+        <v>-1.2070000000000001</v>
+      </c>
+      <c r="G30">
+        <v>-1.2110000000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E31">
+        <v>290.5</v>
+      </c>
+      <c r="F31">
+        <v>-1.137</v>
+      </c>
+      <c r="G31">
+        <v>-1.141</v>
+      </c>
+    </row>
+    <row r="32" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E32">
+        <v>300.39999999999998</v>
+      </c>
+      <c r="F32">
+        <v>-1.0660000000000001</v>
+      </c>
+      <c r="G32">
+        <v>-1.071</v>
+      </c>
+    </row>
+    <row r="33" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E33">
+        <v>310.39999999999998</v>
+      </c>
+      <c r="F33">
+        <v>-0.995</v>
+      </c>
+      <c r="G33">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="34" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E34">
+        <v>320.60000000000002</v>
+      </c>
+      <c r="F34">
+        <v>-0.92200000000000004</v>
+      </c>
+      <c r="G34">
+        <v>-0.92700000000000005</v>
+      </c>
+    </row>
+    <row r="35" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E35">
+        <v>330.7</v>
+      </c>
+      <c r="F35">
+        <v>-0.85</v>
+      </c>
+      <c r="G35">
+        <v>-0.85599999999999998</v>
+      </c>
+    </row>
+    <row r="36" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E36">
+        <v>340.7</v>
+      </c>
+      <c r="F36">
+        <v>-0.77900000000000003</v>
+      </c>
+      <c r="G36">
+        <v>-0.78500000000000003</v>
+      </c>
+    </row>
+    <row r="37" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E37">
+        <v>350.9</v>
+      </c>
+      <c r="F37">
+        <v>-0.70599999999999996</v>
+      </c>
+      <c r="G37">
+        <v>-0.71299999999999997</v>
+      </c>
+    </row>
+    <row r="38" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E38">
+        <v>360.7</v>
+      </c>
+      <c r="F38">
+        <v>-0.63600000000000001</v>
+      </c>
+      <c r="G38">
+        <v>-0.64300000000000002</v>
+      </c>
+    </row>
+    <row r="39" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E39">
+        <v>371</v>
+      </c>
+      <c r="F39">
+        <v>-0.56299999999999994</v>
+      </c>
+      <c r="G39">
+        <v>-0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="40" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E40">
+        <v>380.6</v>
+      </c>
+      <c r="F40">
+        <v>-0.49399999999999999</v>
+      </c>
+      <c r="G40">
+        <v>-0.502</v>
+      </c>
+    </row>
+    <row r="41" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E41">
+        <v>391</v>
+      </c>
+      <c r="F41">
+        <v>-0.42</v>
+      </c>
+      <c r="G41">
+        <v>-0.42799999999999999</v>
+      </c>
+    </row>
+    <row r="42" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E42">
+        <v>401.1</v>
+      </c>
+      <c r="F42">
+        <v>-0.34699999999999998</v>
+      </c>
+      <c r="G42">
+        <v>-0.35599999999999998</v>
+      </c>
+    </row>
+    <row r="43" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E43">
+        <v>410.9</v>
+      </c>
+      <c r="F43">
+        <v>-0.27800000000000002</v>
+      </c>
+      <c r="G43">
+        <v>-0.28599999999999998</v>
+      </c>
+    </row>
+    <row r="44" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E44">
+        <v>420.6</v>
+      </c>
+      <c r="F44">
+        <v>-0.21</v>
+      </c>
+      <c r="G44">
+        <v>-0.218</v>
+      </c>
+    </row>
+    <row r="45" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E45">
+        <v>430.8</v>
+      </c>
+      <c r="F45">
+        <v>-0.13700000000000001</v>
+      </c>
+      <c r="G45">
+        <v>-0.14499999999999999</v>
+      </c>
+    </row>
+    <row r="46" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E46">
+        <v>440.7</v>
+      </c>
+      <c r="F46">
+        <v>-6.9000000000000006E-2</v>
+      </c>
+      <c r="G46">
+        <v>-7.5999999999999998E-2</v>
+      </c>
+    </row>
+    <row r="47" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E47">
+        <v>450.6</v>
+      </c>
+      <c r="F47">
+        <v>3.0000000000000001E-3</v>
+      </c>
+      <c r="G47">
+        <v>-6.0000000000000001E-3</v>
+      </c>
+    </row>
+    <row r="48" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E48">
+        <v>460.6</v>
+      </c>
+      <c r="F48">
+        <v>7.3999999999999996E-2</v>
+      </c>
+      <c r="G48">
+        <v>6.8000000000000005E-2</v>
+      </c>
+    </row>
+    <row r="49" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E49">
+        <v>470.8</v>
+      </c>
+      <c r="F49">
+        <v>0.14699999999999999</v>
+      </c>
+      <c r="G49">
+        <v>0.14000000000000001</v>
+      </c>
+    </row>
+    <row r="50" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E50">
+        <v>480.8</v>
+      </c>
+      <c r="F50">
+        <v>0.219</v>
+      </c>
+      <c r="G50">
+        <v>0.20799999999999999</v>
+      </c>
+    </row>
+    <row r="51" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E51">
+        <v>490.7</v>
+      </c>
+      <c r="F51">
+        <v>0.28799999999999998</v>
+      </c>
+      <c r="G51">
+        <v>0.27700000000000002</v>
+      </c>
+    </row>
+    <row r="52" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E52">
+        <v>500.9</v>
+      </c>
+      <c r="F52">
+        <v>0.36199999999999999</v>
+      </c>
+      <c r="G52">
+        <v>0.35</v>
+      </c>
+    </row>
+    <row r="53" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E53">
+        <v>510.8</v>
+      </c>
+      <c r="F53">
+        <v>0.432</v>
+      </c>
+      <c r="G53">
+        <v>0.42</v>
+      </c>
+    </row>
+    <row r="54" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E54">
+        <v>520.70000000000005</v>
+      </c>
+      <c r="F54">
+        <v>0.504</v>
+      </c>
+      <c r="G54">
+        <v>0.49099999999999999</v>
+      </c>
+    </row>
+    <row r="55" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E55">
+        <v>530.5</v>
+      </c>
+      <c r="F55">
+        <v>0.57399999999999995</v>
+      </c>
+      <c r="G55">
+        <v>0.56000000000000005</v>
+      </c>
+    </row>
+    <row r="56" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E56">
+        <v>540.5</v>
+      </c>
+      <c r="F56">
+        <v>0.64500000000000002</v>
+      </c>
+      <c r="G56">
+        <v>0.63</v>
+      </c>
+    </row>
+    <row r="57" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E57">
+        <v>550.29999999999995</v>
+      </c>
+      <c r="F57">
+        <v>0.71499999999999997</v>
+      </c>
+      <c r="G57">
+        <v>0.69899999999999995</v>
+      </c>
+    </row>
+    <row r="58" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E58">
+        <v>560.29999999999995</v>
+      </c>
+      <c r="F58">
+        <v>0.78600000000000003</v>
+      </c>
+      <c r="G58">
+        <v>0.76900000000000002</v>
+      </c>
+    </row>
+    <row r="59" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E59">
+        <v>570.4</v>
+      </c>
+      <c r="F59">
+        <v>0.85599999999999998</v>
+      </c>
+      <c r="G59">
+        <v>0.83599999999999997</v>
+      </c>
+    </row>
+    <row r="60" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E60">
+        <v>580.70000000000005</v>
+      </c>
+      <c r="F60">
+        <v>0.92700000000000005</v>
+      </c>
+      <c r="G60">
+        <v>0.9</v>
+      </c>
+    </row>
+    <row r="61" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E61">
+        <v>590.70000000000005</v>
+      </c>
+      <c r="F61">
+        <v>0.99299999999999999</v>
+      </c>
+      <c r="G61">
+        <v>0.95</v>
+      </c>
+    </row>
+    <row r="62" spans="5:7" x14ac:dyDescent="0.35">
+      <c r="E62">
+        <v>601</v>
+      </c>
+      <c r="F62">
+        <v>1.052</v>
+      </c>
+      <c r="G62">
+        <v>0.99099999999999999</v>
+      </c>
+    </row>
+    <row r="73" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A73" s="1"/>
+    </row>
+    <row r="74" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A74">
+        <f>-0.637*100.02+449.98</f>
+        <v>386.26726000000002</v>
+      </c>
+    </row>
+    <row r="79" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A79" t="s">
         <v>2</v>
       </c>
-      <c r="B28" t="s">
+      <c r="B79" t="s">
         <v>3</v>
       </c>
-      <c r="C28" t="s">
+      <c r="C79" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A29">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A80">
         <v>0</v>
       </c>
-      <c r="B29">
+      <c r="B80">
         <v>-5</v>
       </c>
-      <c r="C29">
+      <c r="C80">
         <v>0</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E80" t="s">
         <v>9</v>
       </c>
-      <c r="G29" t="s">
+      <c r="G80" t="s">
         <v>11</v>
       </c>
     </row>
-    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A30">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A81">
         <f>2^16-1</f>
         <v>65535</v>
       </c>
-      <c r="B30">
+      <c r="B81">
         <v>5</v>
       </c>
-      <c r="C30">
+      <c r="C81">
         <v>1000</v>
       </c>
-      <c r="E30">
-        <f>C30/(A30+1)</f>
+      <c r="E81">
+        <f>C81/(A81+1)</f>
         <v>1.52587890625E-2</v>
       </c>
-      <c r="G30">
-        <f>1/E30</f>
+      <c r="G81">
+        <f>1/E81</f>
         <v>65.536000000000001</v>
       </c>
     </row>
-    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A33" t="s">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A84" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A34">
-        <f>(A30+1)/C30</f>
+    <row r="85" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A85">
+        <f>(A81+1)/C81</f>
         <v>65.536000000000001</v>
       </c>
-      <c r="B34" t="s">
+      <c r="B85" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A36" t="s">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A87" t="s">
         <v>7</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E87" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A37">
-        <f>(A30+1)/(B30-B29)</f>
+    <row r="88" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A88">
+        <f>(A81+1)/(B81-B80)</f>
         <v>6553.6</v>
       </c>
-      <c r="B37" t="s">
+      <c r="B88" t="s">
         <v>8</v>
       </c>
-      <c r="E37">
-        <f>1/A37</f>
+      <c r="E88">
+        <f>1/A88</f>
         <v>1.52587890625E-4</v>
       </c>
     </row>
-    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A39" t="s">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A90" t="s">
         <v>14</v>
       </c>
-      <c r="E39" t="s">
+      <c r="E90" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="E40">
-        <f>A37*0.0025</f>
+    <row r="91" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="E91">
+        <f>A88*0.0025</f>
         <v>16.384</v>
       </c>
     </row>
-    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="G43" t="s">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G94" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="G44">
-        <f>E40/G30</f>
+    <row r="95" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="G95">
+        <f>E91/G81</f>
         <v>0.25</v>
       </c>
     </row>

--- a/docs/volts_to_adc.xlsx
+++ b/docs/volts_to_adc.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26501"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GIT\UltraZohm\pcb_design\uz_per_sic_inverter_828xcc\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C229371-8406-486D-9A94-FB75C02EE40A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AF0820F6-0801-4723-9607-D45A6F6FC208}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{7228B6C1-6041-4CB5-8AFD-AFF5B824FE5A}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="22" uniqueCount="20">
   <si>
     <t>v_dc</t>
   </si>
@@ -90,6 +90,12 @@
   </si>
   <si>
     <t>v_dc multimeter</t>
+  </si>
+  <si>
+    <t>offset</t>
+  </si>
+  <si>
+    <t>pu mit Base 150 V</t>
   </si>
 </sst>
 </file>
@@ -1717,7 +1723,398 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="de-DE"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="de-DE"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:scatterChart>
+        <c:scatterStyle val="lineMarker"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="19050" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:trendline>
+            <c:spPr>
+              <a:ln w="19050" cap="rnd">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+                <a:prstDash val="sysDot"/>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+            <c:trendlineType val="linear"/>
+            <c:dispRSqr val="0"/>
+            <c:dispEq val="1"/>
+            <c:trendlineLbl>
+              <c:numFmt formatCode="General" sourceLinked="0"/>
+              <c:spPr>
+                <a:noFill/>
+                <a:ln>
+                  <a:noFill/>
+                </a:ln>
+                <a:effectLst/>
+              </c:spPr>
+              <c:txPr>
+                <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+                <a:lstStyle/>
+                <a:p>
+                  <a:pPr>
+                    <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                      <a:solidFill>
+                        <a:schemeClr val="tx1">
+                          <a:lumMod val="65000"/>
+                          <a:lumOff val="35000"/>
+                        </a:schemeClr>
+                      </a:solidFill>
+                      <a:latin typeface="+mn-lt"/>
+                      <a:ea typeface="+mn-ea"/>
+                      <a:cs typeface="+mn-cs"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:endParaRPr lang="de-DE"/>
+                </a:p>
+              </c:txPr>
+            </c:trendlineLbl>
+          </c:trendline>
+          <c:xVal>
+            <c:numRef>
+              <c:f>Tabelle1!$B$32:$B$34</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>21845.333333333332</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>19680.480480480477</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>24248.32</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:xVal>
+          <c:yVal>
+            <c:numRef>
+              <c:f>Tabelle1!$C$32:$C$34</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="3"/>
+                <c:pt idx="0">
+                  <c:v>1.1100000000000001</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.8</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1.45</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:yVal>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-7F43-4282-B59D-764A57E35E08}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:axId val="2072405504"/>
+        <c:axId val="2072406464"/>
+      </c:scatterChart>
+      <c:valAx>
+        <c:axId val="2072405504"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2072406464"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="2072406464"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="25000"/>
+                <a:lumOff val="75000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="de-DE"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2072405504"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="midCat"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="de-DE"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.78740157499999996" l="0.7" r="0.7" t="0.78740157499999996" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors2.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
   <a:schemeClr val="accent2"/>
@@ -2273,20 +2670,536 @@
 </cs:chartStyle>
 </file>
 
+<file path=xl/charts/style2.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="240">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="50000"/>
+            <a:lumOff val="50000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>1</xdr:row>
-      <xdr:rowOff>122237</xdr:rowOff>
+      <xdr:colOff>422275</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>65087</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>57151</xdr:colOff>
-      <xdr:row>23</xdr:row>
-      <xdr:rowOff>101601</xdr:rowOff>
+      <xdr:colOff>482601</xdr:colOff>
+      <xdr:row>26</xdr:row>
+      <xdr:rowOff>44451</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -2306,6 +3219,42 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>114300</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>396875</xdr:colOff>
+      <xdr:row>40</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="Diagramm 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1890F7F0-A7AD-1A28-CCCB-1605CC54590D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -2616,7 +3565,7 @@
   <cols>
     <col min="2" max="2" width="19.08984375" customWidth="1"/>
     <col min="3" max="3" width="22.81640625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.54296875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.81640625" bestFit="1" customWidth="1"/>
     <col min="6" max="7" width="22.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2895,7 +3844,7 @@
         <v>-2.2050000000000001</v>
       </c>
     </row>
-    <row r="17" spans="5:7" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
       <c r="E17">
         <v>150.80000000000001</v>
       </c>
@@ -2906,7 +3855,7 @@
         <v>-2.1349999999999998</v>
       </c>
     </row>
-    <row r="18" spans="5:7" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="E18">
         <v>160.80000000000001</v>
       </c>
@@ -2917,7 +3866,7 @@
         <v>-2.0630000000000002</v>
       </c>
     </row>
-    <row r="19" spans="5:7" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
       <c r="E19">
         <v>171</v>
       </c>
@@ -2928,7 +3877,7 @@
         <v>-1.9910000000000001</v>
       </c>
     </row>
-    <row r="20" spans="5:7" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
       <c r="E20">
         <v>181</v>
       </c>
@@ -2939,7 +3888,7 @@
         <v>-1.92</v>
       </c>
     </row>
-    <row r="21" spans="5:7" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
       <c r="E21">
         <v>190.9</v>
       </c>
@@ -2950,7 +3899,7 @@
         <v>-1.849</v>
       </c>
     </row>
-    <row r="22" spans="5:7" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.35">
       <c r="E22">
         <v>200.8</v>
       </c>
@@ -2961,7 +3910,7 @@
         <v>-1.7789999999999999</v>
       </c>
     </row>
-    <row r="23" spans="5:7" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.35">
       <c r="E23">
         <v>211</v>
       </c>
@@ -2972,7 +3921,7 @@
         <v>-1.706</v>
       </c>
     </row>
-    <row r="24" spans="5:7" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.35">
       <c r="E24">
         <v>220.9</v>
       </c>
@@ -2983,7 +3932,7 @@
         <v>-1.635</v>
       </c>
     </row>
-    <row r="25" spans="5:7" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.35">
       <c r="E25">
         <v>230.9</v>
       </c>
@@ -2994,7 +3943,7 @@
         <v>-1.5640000000000001</v>
       </c>
     </row>
-    <row r="26" spans="5:7" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.35">
       <c r="E26">
         <v>241.1</v>
       </c>
@@ -3005,7 +3954,7 @@
         <v>-1.492</v>
       </c>
     </row>
-    <row r="27" spans="5:7" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.35">
       <c r="E27">
         <v>251</v>
       </c>
@@ -3016,7 +3965,7 @@
         <v>-1.421</v>
       </c>
     </row>
-    <row r="28" spans="5:7" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.35">
       <c r="E28">
         <v>260.8</v>
       </c>
@@ -3027,7 +3976,7 @@
         <v>-1.3520000000000001</v>
       </c>
     </row>
-    <row r="29" spans="5:7" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.35">
       <c r="E29">
         <v>270.60000000000002</v>
       </c>
@@ -3038,7 +3987,16 @@
         <v>-1.2829999999999999</v>
       </c>
     </row>
-    <row r="30" spans="5:7" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A30" t="s">
+        <v>4</v>
+      </c>
+      <c r="B30" t="s">
+        <v>18</v>
+      </c>
+      <c r="C30" t="s">
+        <v>19</v>
+      </c>
       <c r="E30">
         <v>280.7</v>
       </c>
@@ -3049,7 +4007,16 @@
         <v>-1.2110000000000001</v>
       </c>
     </row>
-    <row r="31" spans="5:7" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A31">
+        <v>150</v>
+      </c>
+      <c r="B31">
+        <v>32768</v>
+      </c>
+      <c r="C31">
+        <v>1.32</v>
+      </c>
       <c r="E31">
         <v>290.5</v>
       </c>
@@ -3060,7 +4027,17 @@
         <v>-1.141</v>
       </c>
     </row>
-    <row r="32" spans="5:7" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A32">
+        <v>150</v>
+      </c>
+      <c r="B32">
+        <f>B31/3*2</f>
+        <v>21845.333333333332</v>
+      </c>
+      <c r="C32">
+        <v>1.1100000000000001</v>
+      </c>
       <c r="E32">
         <v>300.39999999999998</v>
       </c>
@@ -3071,7 +4048,17 @@
         <v>-1.071</v>
       </c>
     </row>
-    <row r="33" spans="5:7" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A33">
+        <v>150</v>
+      </c>
+      <c r="B33">
+        <f>B32/C32</f>
+        <v>19680.480480480477</v>
+      </c>
+      <c r="C33">
+        <v>0.8</v>
+      </c>
       <c r="E33">
         <v>310.39999999999998</v>
       </c>
@@ -3082,7 +4069,17 @@
         <v>-1</v>
       </c>
     </row>
-    <row r="34" spans="5:7" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A34">
+        <v>150</v>
+      </c>
+      <c r="B34">
+        <f>B32*C32</f>
+        <v>24248.32</v>
+      </c>
+      <c r="C34">
+        <v>1.45</v>
+      </c>
       <c r="E34">
         <v>320.60000000000002</v>
       </c>
@@ -3093,7 +4090,7 @@
         <v>-0.92700000000000005</v>
       </c>
     </row>
-    <row r="35" spans="5:7" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:7" x14ac:dyDescent="0.35">
       <c r="E35">
         <v>330.7</v>
       </c>
@@ -3104,7 +4101,7 @@
         <v>-0.85599999999999998</v>
       </c>
     </row>
-    <row r="36" spans="5:7" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:7" x14ac:dyDescent="0.35">
       <c r="E36">
         <v>340.7</v>
       </c>
@@ -3115,7 +4112,7 @@
         <v>-0.78500000000000003</v>
       </c>
     </row>
-    <row r="37" spans="5:7" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:7" x14ac:dyDescent="0.35">
       <c r="E37">
         <v>350.9</v>
       </c>
@@ -3126,7 +4123,13 @@
         <v>-0.71299999999999997</v>
       </c>
     </row>
-    <row r="38" spans="5:7" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B38">
+        <v>21000</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
       <c r="E38">
         <v>360.7</v>
       </c>
@@ -3137,7 +4140,7 @@
         <v>-0.64300000000000002</v>
       </c>
     </row>
-    <row r="39" spans="5:7" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:7" x14ac:dyDescent="0.35">
       <c r="E39">
         <v>371</v>
       </c>
@@ -3148,7 +4151,7 @@
         <v>-0.56999999999999995</v>
       </c>
     </row>
-    <row r="40" spans="5:7" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:7" x14ac:dyDescent="0.35">
       <c r="E40">
         <v>380.6</v>
       </c>
@@ -3159,7 +4162,11 @@
         <v>-0.502</v>
       </c>
     </row>
-    <row r="41" spans="5:7" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B41">
+        <f>1/565</f>
+        <v>1.7699115044247787E-3</v>
+      </c>
       <c r="E41">
         <v>391</v>
       </c>
@@ -3170,7 +4177,7 @@
         <v>-0.42799999999999999</v>
       </c>
     </row>
-    <row r="42" spans="5:7" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:7" x14ac:dyDescent="0.35">
       <c r="E42">
         <v>401.1</v>
       </c>
@@ -3181,7 +4188,11 @@
         <v>-0.35599999999999998</v>
       </c>
     </row>
-    <row r="43" spans="5:7" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="B43">
+        <f>565/2</f>
+        <v>282.5</v>
+      </c>
       <c r="E43">
         <v>410.9</v>
       </c>
@@ -3192,7 +4203,7 @@
         <v>-0.28599999999999998</v>
       </c>
     </row>
-    <row r="44" spans="5:7" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:7" x14ac:dyDescent="0.35">
       <c r="E44">
         <v>420.6</v>
       </c>
@@ -3203,7 +4214,7 @@
         <v>-0.218</v>
       </c>
     </row>
-    <row r="45" spans="5:7" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:7" x14ac:dyDescent="0.35">
       <c r="E45">
         <v>430.8</v>
       </c>
@@ -3214,7 +4225,7 @@
         <v>-0.14499999999999999</v>
       </c>
     </row>
-    <row r="46" spans="5:7" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:7" x14ac:dyDescent="0.35">
       <c r="E46">
         <v>440.7</v>
       </c>
@@ -3225,7 +4236,7 @@
         <v>-7.5999999999999998E-2</v>
       </c>
     </row>
-    <row r="47" spans="5:7" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:7" x14ac:dyDescent="0.35">
       <c r="E47">
         <v>450.6</v>
       </c>
@@ -3236,7 +4247,7 @@
         <v>-6.0000000000000001E-3</v>
       </c>
     </row>
-    <row r="48" spans="5:7" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:7" x14ac:dyDescent="0.35">
       <c r="E48">
         <v>460.6</v>
       </c>
